--- a/data/WP18_auswertung_ministerien.xlsx
+++ b/data/WP18_auswertung_ministerien.xlsx
@@ -1002,13 +1002,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB4A0713-88DC-4CD9-839C-E32999E05C53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A18895E6-A302-4BED-B95C-16466695417C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D2C0D19-D84C-4D14-BFD8-D6AE112FCAFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C610B7C7-89D5-449A-A36B-F0A7A7E48E7E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30E2F1D7-5D72-40F1-B21D-03A8A201ACB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DC9ABF8-9E3F-4A77-AEFA-BA4E4824B660}"/>
 </file>